--- a/pipeline/tests/fixtures/preseg_batch/manifest.xlsx
+++ b/pipeline/tests/fixtures/preseg_batch/manifest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,15 +494,20 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>entity_types</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>file_no</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>source_created_by</t>
         </is>
@@ -582,11 +587,16 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>证券公司;证券从业人员</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>招揽;展业</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>kb_admin</t>
         </is>
@@ -664,17 +674,18 @@
           <t>公司级</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>合规</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>ZD-2024-005</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>kb_admin</t>
         </is>

--- a/pipeline/tests/fixtures/preseg_batch/manifest.xlsx
+++ b/pipeline/tests/fixtures/preseg_batch/manifest.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manifest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,16 @@
           <t>source_created_by</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>source_law_id</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>invalid_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -564,7 +574,6 @@
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>KB-EXT-0001</t>
@@ -595,10 +604,14 @@
           <t>招揽;展业</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>kb_admin</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>KB-EXT-0000-PRE</t>
         </is>
       </c>
     </row>
@@ -653,7 +666,6 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>KB-INT-0001</t>
@@ -674,7 +686,6 @@
           <t>公司级</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>合规</t>
@@ -688,6 +699,11 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>kb_admin</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
